--- a/backend/toolbox/股票pre估值.xlsx
+++ b/backend/toolbox/股票pre估值.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t>个股</t>
   </si>
@@ -203,6 +203,396 @@
   </si>
   <si>
     <t>20260815</t>
+  </si>
+  <si>
+    <t>20260817</t>
+  </si>
+  <si>
+    <t>171.38</t>
+  </si>
+  <si>
+    <t>1011.75</t>
+  </si>
+  <si>
+    <t>20260818</t>
+  </si>
+  <si>
+    <t>155.62</t>
+  </si>
+  <si>
+    <t>940.76</t>
+  </si>
+  <si>
+    <t>20260819</t>
+  </si>
+  <si>
+    <t>156.16</t>
+  </si>
+  <si>
+    <t>937.105</t>
+  </si>
+  <si>
+    <t>20260820</t>
+  </si>
+  <si>
+    <t>163.08</t>
+  </si>
+  <si>
+    <t>974.33</t>
+  </si>
+  <si>
+    <t>20260821</t>
+  </si>
+  <si>
+    <t>163.41</t>
+  </si>
+  <si>
+    <t>966.78</t>
+  </si>
+  <si>
+    <t>20260822</t>
+  </si>
+  <si>
+    <t>20260824</t>
+  </si>
+  <si>
+    <t>155.37</t>
+  </si>
+  <si>
+    <t>910.43</t>
+  </si>
+  <si>
+    <t>20260825</t>
+  </si>
+  <si>
+    <t>158.02</t>
+  </si>
+  <si>
+    <t>938.4</t>
+  </si>
+  <si>
+    <t>20260827</t>
+  </si>
+  <si>
+    <t>161.04</t>
+  </si>
+  <si>
+    <t>932.86</t>
+  </si>
+  <si>
+    <t>20260829</t>
+  </si>
+  <si>
+    <t>164.58</t>
+  </si>
+  <si>
+    <t>958.73</t>
+  </si>
+  <si>
+    <t>20260901</t>
+  </si>
+  <si>
+    <t>160.78</t>
+  </si>
+  <si>
+    <t>933.44</t>
+  </si>
+  <si>
+    <t>20260902</t>
+  </si>
+  <si>
+    <t>164.98</t>
+  </si>
+  <si>
+    <t>956.08</t>
+  </si>
+  <si>
+    <t>20260903</t>
+  </si>
+  <si>
+    <t>177.0</t>
+  </si>
+  <si>
+    <t>1016.59</t>
+  </si>
+  <si>
+    <t>20260905</t>
+  </si>
+  <si>
+    <t>20260907</t>
+  </si>
+  <si>
+    <t>20260908</t>
+  </si>
+  <si>
+    <t>188.585</t>
+  </si>
+  <si>
+    <t>1023.56</t>
+  </si>
+  <si>
+    <t>20260909</t>
+  </si>
+  <si>
+    <t>185.55</t>
+  </si>
+  <si>
+    <t>1000.26</t>
+  </si>
+  <si>
+    <t>195.38</t>
+  </si>
+  <si>
+    <t>1037.96</t>
+  </si>
+  <si>
+    <t>198.63</t>
+  </si>
+  <si>
+    <t>1027.77</t>
+  </si>
+  <si>
+    <t>20260910</t>
+  </si>
+  <si>
+    <t>188.3</t>
+  </si>
+  <si>
+    <t>977.41</t>
+  </si>
+  <si>
+    <t>20260911</t>
+  </si>
+  <si>
+    <t>190.07</t>
+  </si>
+  <si>
+    <t>975.26</t>
+  </si>
+  <si>
+    <t>20260913</t>
+  </si>
+  <si>
+    <t>20260914</t>
+  </si>
+  <si>
+    <t>175.63</t>
+  </si>
+  <si>
+    <t>924.03</t>
+  </si>
+  <si>
+    <t>20260915</t>
+  </si>
+  <si>
+    <t>174.83</t>
+  </si>
+  <si>
+    <t>927.6</t>
+  </si>
+  <si>
+    <t>20260916</t>
+  </si>
+  <si>
+    <t>182.99</t>
+  </si>
+  <si>
+    <t>977.5</t>
+  </si>
+  <si>
+    <t>20260918</t>
+  </si>
+  <si>
+    <t>185.335</t>
+  </si>
+  <si>
+    <t>989.54</t>
+  </si>
+  <si>
+    <t>187.5</t>
+  </si>
+  <si>
+    <t>1015.8</t>
+  </si>
+  <si>
+    <t>20260919</t>
+  </si>
+  <si>
+    <t>20260921</t>
+  </si>
+  <si>
+    <t>186.88</t>
+  </si>
+  <si>
+    <t>1041.21</t>
+  </si>
+  <si>
+    <t>188.86</t>
+  </si>
+  <si>
+    <t>1043.96</t>
+  </si>
+  <si>
+    <t>20260922</t>
+  </si>
+  <si>
+    <t>195.37</t>
+  </si>
+  <si>
+    <t>1096.16</t>
+  </si>
+  <si>
+    <t>20260923</t>
+  </si>
+  <si>
+    <t>185.56</t>
+  </si>
+  <si>
+    <t>1056.2093</t>
+  </si>
+  <si>
+    <t>20260924</t>
+  </si>
+  <si>
+    <t>186.37</t>
+  </si>
+  <si>
+    <t>1080.53</t>
+  </si>
+  <si>
+    <t>20260925</t>
+  </si>
+  <si>
+    <t>191.56</t>
+  </si>
+  <si>
+    <t>1082.28</t>
+  </si>
+  <si>
+    <t>20260926</t>
+  </si>
+  <si>
+    <t>186.68</t>
+  </si>
+  <si>
+    <t>1065.08</t>
+  </si>
+  <si>
+    <t>20260930</t>
+  </si>
+  <si>
+    <t>184.15</t>
+  </si>
+  <si>
+    <t>1065.11</t>
+  </si>
+  <si>
+    <t>20261001</t>
+  </si>
+  <si>
+    <t>188.955</t>
+  </si>
+  <si>
+    <t>1065.59</t>
+  </si>
+  <si>
+    <t>20261006</t>
+  </si>
+  <si>
+    <t>178.25</t>
+  </si>
+  <si>
+    <t>1088.0</t>
+  </si>
+  <si>
+    <t>20261008</t>
+  </si>
+  <si>
+    <t>169.03</t>
+  </si>
+  <si>
+    <t>1029.0</t>
+  </si>
+  <si>
+    <t>20261012</t>
+  </si>
+  <si>
+    <t>162.23</t>
+  </si>
+  <si>
+    <t>989.04</t>
+  </si>
+  <si>
+    <t>20261013</t>
+  </si>
+  <si>
+    <t>154.58</t>
+  </si>
+  <si>
+    <t>938.6</t>
+  </si>
+  <si>
+    <t>157.06</t>
+  </si>
+  <si>
+    <t>953.19</t>
+  </si>
+  <si>
+    <t>20261014</t>
+  </si>
+  <si>
+    <t>147.55</t>
+  </si>
+  <si>
+    <t>914.13</t>
+  </si>
+  <si>
+    <t>20261015</t>
+  </si>
+  <si>
+    <t>140.1</t>
+  </si>
+  <si>
+    <t>864.77</t>
+  </si>
+  <si>
+    <t>146.11</t>
+  </si>
+  <si>
+    <t>931.24</t>
+  </si>
+  <si>
+    <t>20261016</t>
+  </si>
+  <si>
+    <t>136.49</t>
+  </si>
+  <si>
+    <t>878.84</t>
+  </si>
+  <si>
+    <t>20261017</t>
+  </si>
+  <si>
+    <t>20261019</t>
+  </si>
+  <si>
+    <t>142.87</t>
+  </si>
+  <si>
+    <t>904.9</t>
+  </si>
+  <si>
+    <t>20261020</t>
+  </si>
+  <si>
+    <t>131.69</t>
+  </si>
+  <si>
+    <t>856.49</t>
+  </si>
+  <si>
+    <t>20261023</t>
   </si>
 </sst>
 </file>
@@ -783,7 +1173,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="E4">
         <v>72.89</v>
@@ -819,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="E5">
         <v>11.29</v>
@@ -866,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
       <c r="F9" s="3"/>
     </row>
